--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50699,8 +50699,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -50723,6 +50723,9 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -50790,6 +50793,21 @@
       </xsd:complexType>
     </xsd:element>
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -50944,10 +50962,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DCAF97-97BE-4522-A6B5-B3CA683DFD68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E64DECC3-3941-40E0-BEDA-F36F17B9A058}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3E86F27-EF3F-4FE7-BBDC-C960C2FA6A48}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBEC9052-2B41-4A17-87FA-D12188A64519}"/>
 </file>
--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50699,8 +50699,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -50723,6 +50723,9 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -50790,6 +50793,21 @@
       </xsd:complexType>
     </xsd:element>
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -50945,7 +50963,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DCAF97-97BE-4522-A6B5-B3CA683DFD68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D52EE-EA2F-4E1E-9298-A6183B6A8E5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50699,8 +50699,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -50723,6 +50723,9 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -50790,6 +50793,21 @@
       </xsd:complexType>
     </xsd:element>
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -50944,10 +50962,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DCAF97-97BE-4522-A6B5-B3CA683DFD68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C88158-2C41-4FBF-8A77-6EBF2829D240}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3E86F27-EF3F-4FE7-BBDC-C960C2FA6A48}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA766EA-D58E-40D3-96F6-733480D534EC}"/>
 </file>
--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50962,10 +50962,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D52EE-EA2F-4E1E-9298-A6183B6A8E5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3E86F27-EF3F-4FE7-BBDC-C960C2FA6A48}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB435E8-AC6A-447E-985C-14951AA23F84}"/>
 </file>
--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50962,10 +50962,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D52EE-EA2F-4E1E-9298-A6183B6A8E5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3E86F27-EF3F-4FE7-BBDC-C960C2FA6A48}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057ADA24-273F-4EC6-B01D-AD44B4EFE4D1}"/>
 </file>
--- a/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
+++ b/Chen_Wiens_2020/41467_2020_14356_MOESM6_ESM.xlsx
@@ -50962,10 +50962,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813D52EE-EA2F-4E1E-9298-A6183B6A8E5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3E86F27-EF3F-4FE7-BBDC-C960C2FA6A48}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6DA6F3F-1C88-439C-88F5-410DD89F6ADE}"/>
 </file>